--- a/public/exports/29189498.xlsx
+++ b/public/exports/29189498.xlsx
@@ -81,16 +81,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202337</t>
+          <t xml:space="preserve">10230750</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F2">
-        <v>1055</v>
+        <v>785</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202337</t>
+          <t xml:space="preserve">1406553, 100980329</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F3">
-        <v>1055</v>
+        <v>1272</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202337</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F4">
-        <v>1127</v>
+        <v>268</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202337</t>
+          <t xml:space="preserve">3148020</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>1530</v>
+        <v>308</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202337, 100800984</t>
+          <t xml:space="preserve">3190298</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F6">
-        <v>627</v>
+        <v>270</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">10230750</t>
+          <t xml:space="preserve">3190971</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F7">
-        <v>785</v>
+        <v>984</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406553, 100980329</t>
+          <t xml:space="preserve">3190971</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F8">
-        <v>1272</v>
+        <v>836</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">401474</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F9">
-        <v>268</v>
+        <v>356</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3148020</t>
+          <t xml:space="preserve">401477, 401478</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="F10">
-        <v>308</v>
+        <v>1284</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180907</t>
+          <t xml:space="preserve">401514, 401515</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F11">
-        <v>2749</v>
+        <v>1029</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180907</t>
+          <t xml:space="preserve">402079</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F12">
-        <v>370</v>
+        <v>788</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180907</t>
+          <t xml:space="preserve">402079</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F13">
-        <v>1074</v>
+        <v>662</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190298</t>
+          <t xml:space="preserve">402771</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F14">
-        <v>270</v>
+        <v>323</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190971</t>
+          <t xml:space="preserve">403766, 403767, 403768, 403769</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>984</v>
+        <v>5954</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190971</t>
+          <t xml:space="preserve">404174</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>836</v>
+        <v>2096</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">402771</t>
+          <t xml:space="preserve">404688</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F17">
-        <v>323</v>
+        <v>1223</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520436</t>
+          <t xml:space="preserve">5533954</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F26">
-        <v>792</v>
+        <v>291</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5533954</t>
+          <t xml:space="preserve">749414, 5514776</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F27">
-        <v>291</v>
+        <v>1504</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1386,11 +1386,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F28">
-        <v>1504</v>
+        <v>2373</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">749414, 5514776</t>
+          <t xml:space="preserve">749442, 5514563</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F29">
-        <v>2373</v>
+        <v>850</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">749442, 5514563</t>
+          <t xml:space="preserve">749493, 5518728</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>850</v>
+        <v>484</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">749486, 5518899</t>
+          <t xml:space="preserve">749493, 5518728</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F31">
-        <v>2244</v>
+        <v>1419</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">749487, 5518901</t>
+          <t xml:space="preserve">749493, 5518728</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F32">
-        <v>2270</v>
+        <v>1128</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">749488, 5518904</t>
+          <t xml:space="preserve">749495, 3144736</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F33">
-        <v>1046</v>
+        <v>479</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">749493, 5518728</t>
+          <t xml:space="preserve">749497, 8580641</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F34">
-        <v>484</v>
+        <v>418</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">749493, 5518728</t>
+          <t xml:space="preserve">749512, 5517645</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>1419</v>
+        <v>1226</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">749493, 5518728</t>
+          <t xml:space="preserve">749809, 3148316</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F36">
-        <v>1128</v>
+        <v>269</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">749495, 3144736</t>
+          <t xml:space="preserve">749905, 8580641</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F37">
-        <v>479</v>
+        <v>434</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">749497, 8580641</t>
+          <t xml:space="preserve">749923, 3141719</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F38">
-        <v>418</v>
+        <v>387</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">749512, 5517645</t>
+          <t xml:space="preserve">750266, 1808753</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F39">
-        <v>1226</v>
+        <v>953</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">749790, 10202337</t>
+          <t xml:space="preserve">750266, 1808753</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F40">
-        <v>531</v>
+        <v>1249</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">749809, 3148316</t>
+          <t xml:space="preserve">750266, 1808753</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F41">
-        <v>269</v>
+        <v>802</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">749905, 8580641</t>
+          <t xml:space="preserve">750295, 3152268</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F42">
-        <v>434</v>
+        <v>509</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">749923, 3141719</t>
+          <t xml:space="preserve">750304, 5533325</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F43">
-        <v>387</v>
+        <v>308</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">750051, 10202337</t>
+          <t xml:space="preserve">750345, 3151979</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F44">
-        <v>306</v>
+        <v>258</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,16 +2231,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">750266, 1808753</t>
+          <t xml:space="preserve">750361, 3152091</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F45">
-        <v>953</v>
+        <v>252</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">750266, 1808753</t>
+          <t xml:space="preserve">750421, 7756595</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F46">
-        <v>1249</v>
+        <v>271</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">750266, 1808753</t>
+          <t xml:space="preserve">750472, 5536592</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>802</v>
+        <v>330</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,16 +2381,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">750295, 3152268</t>
+          <t xml:space="preserve">750730, 1406553</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F48">
-        <v>509</v>
+        <v>902</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">750304, 5533325</t>
+          <t xml:space="preserve">8504629</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>308</v>
+        <v>3954</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">750345, 3151979</t>
+          <t xml:space="preserve">8580639</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F50">
-        <v>258</v>
+        <v>404</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">750358, 7068864</t>
+          <t xml:space="preserve">8580639</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F51">
-        <v>2348</v>
+        <v>404</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,16 +2581,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">750361, 3152091</t>
+          <t xml:space="preserve">8580639</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F52">
-        <v>252</v>
+        <v>404</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">750421, 7756595</t>
+          <t xml:space="preserve">8671728</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>271</v>
+        <v>2708</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">750452, 3180907</t>
+          <t xml:space="preserve">9285142</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F54">
-        <v>381</v>
+        <v>4093</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">750472, 5536592</t>
+          <t xml:space="preserve">9772295</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="F55">
-        <v>330</v>
+        <v>630</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">750730, 1406553</t>
+          <t xml:space="preserve">9772295</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F56">
-        <v>902</v>
+        <v>550</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8504629</t>
+          <t xml:space="preserve">9772295</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F57">
-        <v>3954</v>
+        <v>1296</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2881,16 +2881,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8580639</t>
+          <t xml:space="preserve">9772295</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F58">
-        <v>404</v>
+        <v>270</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,16 +2931,16 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8580639</t>
+          <t xml:space="preserve">9772295</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F59">
-        <v>404</v>
+        <v>275</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2981,30 +2981,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">8580639</t>
+          <t xml:space="preserve">5520436</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F60">
-        <v>404</v>
+        <v>792</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017534</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-14</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8671728</t>
+          <t xml:space="preserve">5510540</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="F61">
-        <v>2708</v>
+        <v>330</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200018868</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-19</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3081,30 +3081,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9285142</t>
+          <t xml:space="preserve">3180907</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62">
-        <v>4093</v>
+        <v>2749</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022071</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3131,30 +3131,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9772295</t>
+          <t xml:space="preserve">3180907</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F63">
-        <v>630</v>
+        <v>370</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022071</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3181,30 +3181,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9772295</t>
+          <t xml:space="preserve">3180907</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F64">
-        <v>550</v>
+        <v>1074</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022071</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3231,30 +3231,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9772295</t>
+          <t xml:space="preserve">750452, 3180907</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F65">
-        <v>1296</v>
+        <v>381</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022071</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3281,30 +3281,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9772295</t>
+          <t xml:space="preserve">8580658</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F66">
-        <v>270</v>
+        <v>1699</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311183386</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3331,30 +3331,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9772295</t>
+          <t xml:space="preserve">8580658</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F67">
-        <v>275</v>
+        <v>5682</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311183386</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3381,35 +3381,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196599</t>
+          <t xml:space="preserve">8019409</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F68">
-        <v>439</v>
+        <v>704</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015799</t>
+          <t xml:space="preserve">311229166</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-24</t>
+          <t xml:space="preserve">2027-02-17</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5510540</t>
+          <t xml:space="preserve">5515247</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,26 +3440,26 @@
         </is>
       </c>
       <c r="F69">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018868</t>
+          <t xml:space="preserve">311232418</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-19</t>
+          <t xml:space="preserve">2027-03-07</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3481,35 +3481,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">404688</t>
+          <t xml:space="preserve">7006145</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>1223</v>
+        <v>3471</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029650</t>
+          <t xml:space="preserve">311233997</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-24</t>
+          <t xml:space="preserve">2027-03-14</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3531,35 +3531,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">401474</t>
+          <t xml:space="preserve">7006145</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F71">
-        <v>356</v>
+        <v>539</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311036858</t>
+          <t xml:space="preserve">311233986</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-02-05</t>
+          <t xml:space="preserve">2027-03-14</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8580658</t>
+          <t xml:space="preserve">3190971</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,26 +3590,26 @@
         </is>
       </c>
       <c r="F72">
-        <v>1699</v>
+        <v>1694</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183386</t>
+          <t xml:space="preserve">311234886</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-15</t>
+          <t xml:space="preserve">2027-03-17</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3631,35 +3631,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8580658</t>
+          <t xml:space="preserve">3197319</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F73">
-        <v>5682</v>
+        <v>3135</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183386</t>
+          <t xml:space="preserve">311236938</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-15</t>
+          <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8019409</t>
+          <t xml:space="preserve">7002091</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="F74">
-        <v>704</v>
+        <v>322</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229166</t>
+          <t xml:space="preserve">311236928</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-17</t>
+          <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5515247</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3740,16 +3740,16 @@
         </is>
       </c>
       <c r="F75">
-        <v>312</v>
+        <v>1375</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311232418</t>
+          <t xml:space="preserve">311242035</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-07</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006145</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F76">
-        <v>3471</v>
+        <v>516</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233997</t>
+          <t xml:space="preserve">311242033</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-14</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006145</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F77">
-        <v>539</v>
+        <v>1300</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233986</t>
+          <t xml:space="preserve">311242036</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-14</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190971</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F78">
-        <v>1694</v>
+        <v>1564</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234886</t>
+          <t xml:space="preserve">311242034</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-17</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3197319</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F79">
-        <v>3135</v>
+        <v>1241</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236938</t>
+          <t xml:space="preserve">311242038</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-27</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7002091</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F80">
-        <v>322</v>
+        <v>259</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236928</t>
+          <t xml:space="preserve">311242031</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-27</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">9285142</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="F81">
-        <v>1375</v>
+        <v>839</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242035</t>
+          <t xml:space="preserve">311243218</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">3194478</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="F82">
-        <v>516</v>
+        <v>306</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242033</t>
+          <t xml:space="preserve">311247877</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">3193076</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F83">
-        <v>1300</v>
+        <v>4617</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242036</t>
+          <t xml:space="preserve">311248803</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">3193076</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F84">
-        <v>1564</v>
+        <v>360</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242034</t>
+          <t xml:space="preserve">311248804</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">8274738</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F85">
-        <v>1241</v>
+        <v>1056</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242038</t>
+          <t xml:space="preserve">311248805</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">5510796</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>259</v>
+        <v>1418</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242031</t>
+          <t xml:space="preserve">311249789</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,25 +4331,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9285142</t>
+          <t xml:space="preserve">5512953</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F87">
-        <v>839</v>
+        <v>919</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243218</t>
+          <t xml:space="preserve">311249785</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3194478</t>
+          <t xml:space="preserve">5514238</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F88">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247877</t>
+          <t xml:space="preserve">311254530</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3193076</t>
+          <t xml:space="preserve">5514238</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F89">
-        <v>4617</v>
+        <v>1100</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248803</t>
+          <t xml:space="preserve">311254530</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3193076</t>
+          <t xml:space="preserve">5529697</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F90">
-        <v>360</v>
+        <v>488</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248804</t>
+          <t xml:space="preserve">311254528</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8274738</t>
+          <t xml:space="preserve">5515841</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="F91">
-        <v>1056</v>
+        <v>309</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248805</t>
+          <t xml:space="preserve">311255688</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5510796</t>
+          <t xml:space="preserve">5515841</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F92">
-        <v>1418</v>
+        <v>402</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249789</t>
+          <t xml:space="preserve">311255688</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-24</t>
+          <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512953</t>
+          <t xml:space="preserve">8469815</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F93">
-        <v>919</v>
+        <v>788</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249785</t>
+          <t xml:space="preserve">311255690</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-24</t>
+          <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5514238</t>
+          <t xml:space="preserve">3197368</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4690,16 +4690,16 @@
         </is>
       </c>
       <c r="F94">
-        <v>292</v>
+        <v>8714</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254530</t>
+          <t xml:space="preserve">311256859</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-16</t>
+          <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5514238</t>
+          <t xml:space="preserve">3141803</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F95">
-        <v>1100</v>
+        <v>4131</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254530</t>
+          <t xml:space="preserve">311259615</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-16</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5529697</t>
+          <t xml:space="preserve">3141803</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F96">
-        <v>488</v>
+        <v>1383</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254528</t>
+          <t xml:space="preserve">311259615</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-16</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5515841</t>
+          <t xml:space="preserve">3141803</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F97">
-        <v>309</v>
+        <v>567</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255688</t>
+          <t xml:space="preserve">311259615</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5515841</t>
+          <t xml:space="preserve">8504590</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98">
-        <v>402</v>
+        <v>1107</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255688</t>
+          <t xml:space="preserve">311259630</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8469815</t>
+          <t xml:space="preserve">8504590</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F99">
-        <v>788</v>
+        <v>1845</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255690</t>
+          <t xml:space="preserve">311259630</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3197368</t>
+          <t xml:space="preserve">8504590</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F100">
-        <v>8714</v>
+        <v>874</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256859</t>
+          <t xml:space="preserve">311259630</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-27</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">8504590</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F101">
-        <v>1992</v>
+        <v>483</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258072</t>
+          <t xml:space="preserve">311259630</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F102">
-        <v>1106</v>
+        <v>2115</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257823</t>
+          <t xml:space="preserve">311260684</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F103">
-        <v>1300</v>
+        <v>499</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258076</t>
+          <t xml:space="preserve">311260724</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F104">
-        <v>1804</v>
+        <v>843</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258081</t>
+          <t xml:space="preserve">311260707</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F105">
-        <v>433</v>
+        <v>539</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258088</t>
+          <t xml:space="preserve">311260710</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F106">
-        <v>433</v>
+        <v>1207</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258094</t>
+          <t xml:space="preserve">311260714</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3141803</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F107">
-        <v>4131</v>
+        <v>1658</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259615</t>
+          <t xml:space="preserve">311260716</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3141803</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F108">
-        <v>1383</v>
+        <v>1987</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259615</t>
+          <t xml:space="preserve">311260718</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3141803</t>
+          <t xml:space="preserve">3190298</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F109">
-        <v>567</v>
+        <v>1742</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259615</t>
+          <t xml:space="preserve">311261818</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-20</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8504590</t>
+          <t xml:space="preserve">3180907</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F110">
-        <v>1107</v>
+        <v>1220</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259630</t>
+          <t xml:space="preserve">311262055</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8504590</t>
+          <t xml:space="preserve">3190217</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="F111">
-        <v>1845</v>
+        <v>629</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259630</t>
+          <t xml:space="preserve">311261981</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8504590</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F112">
-        <v>874</v>
+        <v>1992</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259630</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8504590</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F113">
-        <v>483</v>
+        <v>1106</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259630</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F114">
-        <v>2115</v>
+        <v>1300</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260684</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F115">
-        <v>499</v>
+        <v>1804</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260724</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F116">
-        <v>843</v>
+        <v>433</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260707</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F117">
-        <v>539</v>
+        <v>433</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260710</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5512816</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F118">
-        <v>1207</v>
+        <v>1407</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260714</t>
+          <t xml:space="preserve">311278306</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">7068864</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F119">
-        <v>1658</v>
+        <v>4025</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260716</t>
+          <t xml:space="preserve">311283499</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">750358, 7068864</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F120">
-        <v>1987</v>
+        <v>2348</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260718</t>
+          <t xml:space="preserve">311283502</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190298</t>
+          <t xml:space="preserve">5532250</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>1742</v>
+        <v>5016</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261818</t>
+          <t xml:space="preserve">311286086</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-20</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,25 +6081,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180907</t>
+          <t xml:space="preserve">5532250</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F122">
-        <v>1220</v>
+        <v>1165</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311262055</t>
+          <t xml:space="preserve">311286086</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-21</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190217</t>
+          <t xml:space="preserve">5532250</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F123">
-        <v>629</v>
+        <v>998</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261981</t>
+          <t xml:space="preserve">311286086</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-21</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,25 +6181,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512816</t>
+          <t xml:space="preserve">5532250</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F124">
-        <v>1407</v>
+        <v>2308</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278306</t>
+          <t xml:space="preserve">311286086</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-12</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">7068864</t>
+          <t xml:space="preserve">5532250</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F125">
-        <v>4025</v>
+        <v>368</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283499</t>
+          <t xml:space="preserve">311286112</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-13</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5532250</t>
+          <t xml:space="preserve">5530935</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="F126">
-        <v>5016</v>
+        <v>1108</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286086</t>
+          <t xml:space="preserve">311287044</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5532250</t>
+          <t xml:space="preserve">3196599</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F127">
-        <v>1165</v>
+        <v>439</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286086</t>
+          <t xml:space="preserve">311296066</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2028-02-05</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5532250</t>
+          <t xml:space="preserve">5533338</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F128">
-        <v>998</v>
+        <v>332</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286086</t>
+          <t xml:space="preserve">311309873</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5532250</t>
+          <t xml:space="preserve">5534044</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F129">
-        <v>2308</v>
+        <v>519</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286086</t>
+          <t xml:space="preserve">311309871</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5532250</t>
+          <t xml:space="preserve">5518731</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F130">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286112</t>
+          <t xml:space="preserve">311310833</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2028-04-26</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5530935</t>
+          <t xml:space="preserve">3147782</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="F131">
-        <v>1108</v>
+        <v>1823</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287044</t>
+          <t xml:space="preserve">311323733</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-04</t>
+          <t xml:space="preserve">2028-06-29</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5533338</t>
+          <t xml:space="preserve">5510937</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F132">
-        <v>332</v>
+        <v>2346</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309873</t>
+          <t xml:space="preserve">311325105</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2028-07-06</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5534044</t>
+          <t xml:space="preserve">749486, 5518899</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6640,16 +6640,16 @@
         </is>
       </c>
       <c r="F133">
-        <v>519</v>
+        <v>2244</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309871</t>
+          <t xml:space="preserve">311325408</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2028-07-09</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518731</t>
+          <t xml:space="preserve">749487, 5518901</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F134">
-        <v>406</v>
+        <v>2270</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311310833</t>
+          <t xml:space="preserve">311325422</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-26</t>
+          <t xml:space="preserve">2028-07-09</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3147782</t>
+          <t xml:space="preserve">749488, 5518904</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F135">
-        <v>1823</v>
+        <v>1046</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323733</t>
+          <t xml:space="preserve">311325419</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-29</t>
+          <t xml:space="preserve">2028-07-09</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5510937</t>
+          <t xml:space="preserve">5512231</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F136">
-        <v>2346</v>
+        <v>12599</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311325105</t>
+          <t xml:space="preserve">311486270</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-06</t>
+          <t xml:space="preserve">2031-01-07</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">404174</t>
+          <t xml:space="preserve">7428551</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F137">
-        <v>2096</v>
+        <v>1181</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311341215</t>
+          <t xml:space="preserve">311641669</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-12</t>
+          <t xml:space="preserve">2032-11-09</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512231</t>
+          <t xml:space="preserve">5512255</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="F138">
-        <v>12599</v>
+        <v>2397</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311486270</t>
+          <t xml:space="preserve">311643201</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-07</t>
+          <t xml:space="preserve">2032-11-17</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">402079</t>
+          <t xml:space="preserve">8986950</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c r="F139">
-        <v>788</v>
+        <v>350</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568106</t>
+          <t xml:space="preserve">311645860</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">402079</t>
+          <t xml:space="preserve">5511973</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F140">
-        <v>662</v>
+        <v>362</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568113</t>
+          <t xml:space="preserve">311650125</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">7428551</t>
+          <t xml:space="preserve">100047969</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F141">
-        <v>1181</v>
+        <v>578</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641669</t>
+          <t xml:space="preserve">311650919</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-09</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512255</t>
+          <t xml:space="preserve">100051897</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7090,16 +7090,16 @@
         </is>
       </c>
       <c r="F142">
-        <v>2397</v>
+        <v>1610</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643201</t>
+          <t xml:space="preserve">311650920</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-17</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8986950</t>
+          <t xml:space="preserve">100085261</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="F143">
-        <v>350</v>
+        <v>561</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645860</t>
+          <t xml:space="preserve">311650921</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5511973</t>
+          <t xml:space="preserve">5518900</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F144">
-        <v>362</v>
+        <v>14065</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650125</t>
+          <t xml:space="preserve">311650905</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-19</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047969</t>
+          <t xml:space="preserve">5518015</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F145">
-        <v>578</v>
+        <v>1851</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650919</t>
+          <t xml:space="preserve">311670495</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051897</t>
+          <t xml:space="preserve">5518015</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F146">
-        <v>1610</v>
+        <v>355</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650920</t>
+          <t xml:space="preserve">311670497</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">100085261</t>
+          <t xml:space="preserve">5518894</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,16 +7340,16 @@
         </is>
       </c>
       <c r="F147">
-        <v>561</v>
+        <v>1427</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650921</t>
+          <t xml:space="preserve">311713408</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-10-09</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">401514, 401515</t>
+          <t xml:space="preserve">5530956</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F148">
-        <v>1029</v>
+        <v>1200</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651062</t>
+          <t xml:space="preserve">311714383</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-10-11</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518900</t>
+          <t xml:space="preserve">5511030</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F149">
-        <v>14065</v>
+        <v>458</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650905</t>
+          <t xml:space="preserve">311715531</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-10-17</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518015</t>
+          <t xml:space="preserve">5511948</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="F150">
-        <v>1851</v>
+        <v>368</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670495</t>
+          <t xml:space="preserve">311724881</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-11-27</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518015</t>
+          <t xml:space="preserve">5514206</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F151">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670497</t>
+          <t xml:space="preserve">311731890</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2034-01-05</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">403766, 403767, 403768, 403769</t>
+          <t xml:space="preserve">10202337</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">169</t>
         </is>
       </c>
       <c r="F152">
-        <v>5954</v>
+        <v>1055</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703838</t>
+          <t xml:space="preserve">311762665</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-30</t>
+          <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518894</t>
+          <t xml:space="preserve">10202337</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F153">
-        <v>1427</v>
+        <v>1055</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311713408</t>
+          <t xml:space="preserve">311762665</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-09</t>
+          <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5530956</t>
+          <t xml:space="preserve">10202337</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
       <c r="F154">
-        <v>1200</v>
+        <v>1127</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311714383</t>
+          <t xml:space="preserve">311762665</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-11</t>
+          <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5511030</t>
+          <t xml:space="preserve">10202337</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F155">
-        <v>458</v>
+        <v>1530</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311715531</t>
+          <t xml:space="preserve">311762665</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-17</t>
+          <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5511948</t>
+          <t xml:space="preserve">10202337, 100800984</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="F156">
-        <v>368</v>
+        <v>627</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724881</t>
+          <t xml:space="preserve">311762665</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-27</t>
+          <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">401477, 401478</t>
+          <t xml:space="preserve">749790, 10202337</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F157">
-        <v>1284</v>
+        <v>531</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730087</t>
+          <t xml:space="preserve">311762665</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-19</t>
+          <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5514206</t>
+          <t xml:space="preserve">750051, 10202337</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F158">
-        <v>378</v>
+        <v>306</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731890</t>
+          <t xml:space="preserve">311762665</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-05</t>
+          <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">

--- a/public/exports/29189498.xlsx
+++ b/public/exports/29189498.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjørringvej 176B</t>
+          <t xml:space="preserve">Brombærvej 7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10230750</t>
+          <t xml:space="preserve">3190298</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H2">
-        <v>785</v>
+        <v>270</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjeldgaardsvej 23</t>
+          <t xml:space="preserve">Bundgarnsvej 47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9982</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406553, 100980329</t>
+          <t xml:space="preserve">750361, 3152091</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H3">
-        <v>1272</v>
+        <v>252</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 200</t>
+          <t xml:space="preserve">Buttervej 39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5533954</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H4">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flade Kirkevej 18</t>
+          <t xml:space="preserve">Bådevej 24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9982</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3148020</t>
+          <t xml:space="preserve">750345, 3151979</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H5">
-        <v>308</v>
+        <v>258</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brombærvej 7</t>
+          <t xml:space="preserve">Donbækvej 21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190298</t>
+          <t xml:space="preserve">749414, 5514776</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H6">
-        <v>270</v>
+        <v>1504</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,17 +391,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnevej 6</t>
+          <t xml:space="preserve">Donbækvej 21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">9352</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190971</t>
+          <t xml:space="preserve">749414, 5514776</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -410,7 +410,7 @@
         </is>
       </c>
       <c r="H7">
-        <v>984</v>
+        <v>2373</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,17 +451,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnevej 6</t>
+          <t xml:space="preserve">Drachmannsvej 32</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9352</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190971</t>
+          <t xml:space="preserve">750266, 1808753</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="H8">
-        <v>836</v>
+        <v>953</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivej 4</t>
+          <t xml:space="preserve">Drachmannsvej 32</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">401474</t>
+          <t xml:space="preserve">750266, 1808753</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H9">
-        <v>356</v>
+        <v>1249</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">L.P. Houmøllers Vej 88</t>
+          <t xml:space="preserve">Drachmannsvej 32</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">401477, 401478</t>
+          <t xml:space="preserve">750266, 1808753</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H10">
-        <v>1284</v>
+        <v>802</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anholtvej 4</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">401514, 401515</t>
+          <t xml:space="preserve">5514784</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H11">
-        <v>1029</v>
+        <v>453</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvej 65</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9970</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">402079</t>
+          <t xml:space="preserve">5514784</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H12">
-        <v>788</v>
+        <v>452</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvej 65</t>
+          <t xml:space="preserve">Flade Engvej 8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9970</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">402079</t>
+          <t xml:space="preserve">749493, 5518728</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>662</v>
+        <v>484</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søparken 4</t>
+          <t xml:space="preserve">Flade Engvej 8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">402771</t>
+          <t xml:space="preserve">749493, 5518728</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="H14">
-        <v>323</v>
+        <v>1419</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caspersvej 7</t>
+          <t xml:space="preserve">Flade Engvej 8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">403766, 403767, 403768, 403769</t>
+          <t xml:space="preserve">749493, 5518728</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H15">
-        <v>5954</v>
+        <v>1128</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeborgvej 2</t>
+          <t xml:space="preserve">Flade Kirkevej 18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">404174</t>
+          <t xml:space="preserve">3148020</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="H16">
-        <v>2096</v>
+        <v>308</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Baghs Vej 23A</t>
+          <t xml:space="preserve">Fodboldvej 7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">404688</t>
+          <t xml:space="preserve">749512, 5517645</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H17">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 6</t>
+          <t xml:space="preserve">Havnen 7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512231</t>
+          <t xml:space="preserve">750472, 5536592</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H18">
-        <v>1255</v>
+        <v>330</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhus Alle 102</t>
+          <t xml:space="preserve">Hjørringvej 176B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512231</t>
+          <t xml:space="preserve">10230750</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>2894</v>
+        <v>785</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 16</t>
+          <t xml:space="preserve">Hjørringvej 180A</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512231</t>
+          <t xml:space="preserve">9772295</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H20">
-        <v>3809</v>
+        <v>270</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 14</t>
+          <t xml:space="preserve">Hjørringvej 180A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512231</t>
+          <t xml:space="preserve">9772295</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H21">
-        <v>513</v>
+        <v>275</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 14</t>
+          <t xml:space="preserve">Hjørringvej 180B</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,16 +1301,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512231</t>
+          <t xml:space="preserve">9772295</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H22">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 8</t>
+          <t xml:space="preserve">Hjørringvej 180C</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512231</t>
+          <t xml:space="preserve">9772295</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H23">
-        <v>5207</v>
+        <v>630</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 2</t>
+          <t xml:space="preserve">Hjørringvej 180E</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,16 +1421,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5514784</t>
+          <t xml:space="preserve">9772295</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H24">
-        <v>452</v>
+        <v>1296</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,26 +1471,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 1</t>
+          <t xml:space="preserve">Høvej 64A</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9982</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5514784</t>
+          <t xml:space="preserve">750421, 7756595</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H25">
-        <v>453</v>
+        <v>271</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,26 +1531,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buttervej 39</t>
+          <t xml:space="preserve">Kjeldgaardsvej 23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5533954</t>
+          <t xml:space="preserve">1406553, 100980329</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H26">
-        <v>291</v>
+        <v>1272</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Donbækvej 21</t>
+          <t xml:space="preserve">Kjeldgaardsvej 25</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">749414, 5514776</t>
+          <t xml:space="preserve">750730, 1406553</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="H27">
-        <v>1504</v>
+        <v>902</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Donbækvej 21</t>
+          <t xml:space="preserve">Nordre Strandvej 17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">749414, 5514776</t>
+          <t xml:space="preserve">8580639</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H28">
-        <v>2373</v>
+        <v>404</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrangbækvej 115</t>
+          <t xml:space="preserve">Nordre Strandvej 19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,16 +1721,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">749442, 5514563</t>
+          <t xml:space="preserve">8580639</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H29">
-        <v>850</v>
+        <v>404</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flade Engvej 8</t>
+          <t xml:space="preserve">Nordre Strandvej 21</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">749493, 5518728</t>
+          <t xml:space="preserve">8580639</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="H30">
-        <v>484</v>
+        <v>404</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flade Engvej 8</t>
+          <t xml:space="preserve">Nordre Strandvej 58</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">749493, 5518728</t>
+          <t xml:space="preserve">749905, 8580641</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="H31">
-        <v>1419</v>
+        <v>434</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flade Engvej 8</t>
+          <t xml:space="preserve">Nordre Strandvej 60</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,16 +1901,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">749493, 5518728</t>
+          <t xml:space="preserve">749497, 8580641</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H32">
-        <v>1128</v>
+        <v>418</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skeltvedvej 78</t>
+          <t xml:space="preserve">Parallelvej 14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9970</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">749495, 3144736</t>
+          <t xml:space="preserve">5512231</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H33">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Strandvej 60</t>
+          <t xml:space="preserve">Parallelvej 14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,16 +2021,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">749497, 8580641</t>
+          <t xml:space="preserve">5512231</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H34">
-        <v>418</v>
+        <v>563</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fodboldvej 7</t>
+          <t xml:space="preserve">Parallelvej 16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,16 +2081,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">749512, 5517645</t>
+          <t xml:space="preserve">5512231</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H35">
-        <v>1226</v>
+        <v>3809</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrangbækvej 4C</t>
+          <t xml:space="preserve">Parallelvej 6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,16 +2141,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">749809, 3148316</t>
+          <t xml:space="preserve">5512231</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H36">
-        <v>269</v>
+        <v>1255</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Strandvej 58</t>
+          <t xml:space="preserve">Parallelvej 8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,16 +2201,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">749905, 8580641</t>
+          <t xml:space="preserve">5512231</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H37">
-        <v>434</v>
+        <v>5207</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skydebanevej 28</t>
+          <t xml:space="preserve">Rådhus Alle 102</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,16 +2261,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">749923, 3141719</t>
+          <t xml:space="preserve">5512231</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H38">
-        <v>387</v>
+        <v>2894</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drachmannsvej 32</t>
+          <t xml:space="preserve">Rådhuspladsen 3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">750266, 1808753</t>
+          <t xml:space="preserve">9285142</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H39">
-        <v>953</v>
+        <v>4093</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,26 +2371,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drachmannsvej 32</t>
+          <t xml:space="preserve">Sdr. Havnevej 65</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9982</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">750266, 1808753</t>
+          <t xml:space="preserve">750295, 3152268</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H40">
-        <v>1249</v>
+        <v>509</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drachmannsvej 32</t>
+          <t xml:space="preserve">Skagavej 132A</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,16 +2441,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">750266, 1808753</t>
+          <t xml:space="preserve">8504629</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H41">
-        <v>802</v>
+        <v>3954</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Havnevej 65</t>
+          <t xml:space="preserve">Skarpæsvej 192</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9982</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">750295, 3152268</t>
+          <t xml:space="preserve">750304, 5533325</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H42">
-        <v>509</v>
+        <v>308</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,26 +2551,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skarpæsvej 192</t>
+          <t xml:space="preserve">Skeltvedvej 78</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9970</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">750304, 5533325</t>
+          <t xml:space="preserve">749495, 3144736</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>308</v>
+        <v>479</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,26 +2611,26 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bådevej 24</t>
+          <t xml:space="preserve">Skydebanevej 28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9982</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">750345, 3151979</t>
+          <t xml:space="preserve">749923, 3141719</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>258</v>
+        <v>387</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,26 +2671,26 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bundgarnsvej 47</t>
+          <t xml:space="preserve">Søndergade 200</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9982</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">750361, 3152091</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H45">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvej 64A</t>
+          <t xml:space="preserve">Søparken 4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9982</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">750421, 7756595</t>
+          <t xml:space="preserve">402771</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H46">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,17 +2791,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 7</t>
+          <t xml:space="preserve">Vrangbækvej 115</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">750472, 5536592</t>
+          <t xml:space="preserve">749442, 5514563</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="H47">
-        <v>330</v>
+        <v>850</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,17 +2851,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjeldgaardsvej 25</t>
+          <t xml:space="preserve">Vrangbækvej 4C</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">750730, 1406553</t>
+          <t xml:space="preserve">749809, 3148316</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="H48">
-        <v>902</v>
+        <v>269</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,17 +2911,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagavej 132A</t>
+          <t xml:space="preserve">Ålborgvej 430A</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9352</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8504629</t>
+          <t xml:space="preserve">8671728</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="H49">
-        <v>3954</v>
+        <v>2708</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2971,26 +2971,26 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Strandvej 17</t>
+          <t xml:space="preserve">Ørnevej 6</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9352</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8580639</t>
+          <t xml:space="preserve">3190971</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H50">
-        <v>404</v>
+        <v>984</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,26 +3031,26 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Strandvej 19</t>
+          <t xml:space="preserve">Ørnevej 6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9352</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8580639</t>
+          <t xml:space="preserve">3190971</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H51">
-        <v>404</v>
+        <v>836</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Strandvej 21</t>
+          <t xml:space="preserve">Suensonsvej 1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,30 +3101,30 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8580639</t>
+          <t xml:space="preserve">5520436</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H52">
-        <v>404</v>
+        <v>792</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017534</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-14</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 430A</t>
+          <t xml:space="preserve">Læsøgade 13</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9352</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8671728</t>
+          <t xml:space="preserve">5510540</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="H53">
-        <v>2708</v>
+        <v>330</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200018868</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-19</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspladsen 3</t>
+          <t xml:space="preserve">Østkystvejen 314</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,30 +3221,30 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9285142</t>
+          <t xml:space="preserve">3180907</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>4093</v>
+        <v>2749</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022071</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3271,40 +3271,40 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjørringvej 180C</t>
+          <t xml:space="preserve">Østkystvejen 314</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9772295</t>
+          <t xml:space="preserve">3180907</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H55">
-        <v>630</v>
+        <v>370</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022071</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3331,40 +3331,40 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjørringvej 180B</t>
+          <t xml:space="preserve">Østkystvejen 314</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9772295</t>
+          <t xml:space="preserve">3180907</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H56">
-        <v>550</v>
+        <v>1074</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022071</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3391,40 +3391,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjørringvej 180E</t>
+          <t xml:space="preserve">Østkystvejen 314B</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9772295</t>
+          <t xml:space="preserve">750452, 3180907</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H57">
-        <v>1296</v>
+        <v>381</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022071</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3451,40 +3451,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjørringvej 180A</t>
+          <t xml:space="preserve">Hans Baghs Vej 23A</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9772295</t>
+          <t xml:space="preserve">404688</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H58">
-        <v>270</v>
+        <v>1223</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200029650</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-03-24</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjørringvej 180A</t>
+          <t xml:space="preserve">Mejerivej 4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,30 +3521,30 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9772295</t>
+          <t xml:space="preserve">401474</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H59">
-        <v>275</v>
+        <v>356</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311036858</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-02-05</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suensonsvej 1</t>
+          <t xml:space="preserve">Hånbækvej 32A</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520436</t>
+          <t xml:space="preserve">8580658</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>792</v>
+        <v>1699</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017534</t>
+          <t xml:space="preserve">311183386</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-14</t>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Læsøgade 13</t>
+          <t xml:space="preserve">Hånbækvej 32B</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,25 +3641,25 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5510540</t>
+          <t xml:space="preserve">8580658</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H61">
-        <v>330</v>
+        <v>5682</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018868</t>
+          <t xml:space="preserve">311183386</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-19</t>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østkystvejen 314</t>
+          <t xml:space="preserve">Sæbygårdvej 33</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180907</t>
+          <t xml:space="preserve">8019409</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3710,26 +3710,26 @@
         </is>
       </c>
       <c r="H62">
-        <v>2749</v>
+        <v>704</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022071</t>
+          <t xml:space="preserve">311229166</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-09</t>
+          <t xml:space="preserve">2027-02-17</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3751,45 +3751,45 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østkystvejen 314</t>
+          <t xml:space="preserve">Højrupsvej 2D</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180907</t>
+          <t xml:space="preserve">5515247</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
-        <v>370</v>
+        <v>312</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022071</t>
+          <t xml:space="preserve">311232418</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-09</t>
+          <t xml:space="preserve">2027-03-07</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3811,45 +3811,45 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østkystvejen 314</t>
+          <t xml:space="preserve">Brønderslevvej 99</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180907</t>
+          <t xml:space="preserve">7006145</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H64">
-        <v>1074</v>
+        <v>3471</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022071</t>
+          <t xml:space="preserve">311233997</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-09</t>
+          <t xml:space="preserve">2027-03-14</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3871,45 +3871,45 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østkystvejen 314B</t>
+          <t xml:space="preserve">Brønderslevvej 99</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">750452, 3180907</t>
+          <t xml:space="preserve">7006145</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H65">
-        <v>381</v>
+        <v>539</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022071</t>
+          <t xml:space="preserve">311233986</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-09</t>
+          <t xml:space="preserve">2027-03-14</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hånbækvej 32A</t>
+          <t xml:space="preserve">Ørnevej 6</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9352</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8580658</t>
+          <t xml:space="preserve">3190971</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,26 +3950,26 @@
         </is>
       </c>
       <c r="H66">
-        <v>1699</v>
+        <v>1694</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183386</t>
+          <t xml:space="preserve">311234886</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-15</t>
+          <t xml:space="preserve">2027-03-17</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3991,45 +3991,45 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hånbækvej 32B</t>
+          <t xml:space="preserve">Brolæggervej 4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8580658</t>
+          <t xml:space="preserve">7002091</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H67">
-        <v>5682</v>
+        <v>322</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183386</t>
+          <t xml:space="preserve">311236928</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-15</t>
+          <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæbygårdvej 33</t>
+          <t xml:space="preserve">Rådhusvej 1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8019409</t>
+          <t xml:space="preserve">3197319</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,16 +4070,16 @@
         </is>
       </c>
       <c r="H68">
-        <v>704</v>
+        <v>3135</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229166</t>
+          <t xml:space="preserve">311236938</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-17</t>
+          <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højrupsvej 2D</t>
+          <t xml:space="preserve">Brolæggervej 1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5515247</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="H69">
-        <v>312</v>
+        <v>1375</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311232418</t>
+          <t xml:space="preserve">311242035</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-07</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,35 +4171,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brønderslevvej 99</t>
+          <t xml:space="preserve">Brolæggervej 1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006145</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H70">
-        <v>3471</v>
+        <v>516</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233997</t>
+          <t xml:space="preserve">311242033</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-14</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,35 +4231,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brønderslevvej 99</t>
+          <t xml:space="preserve">Brolæggervej 1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006145</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H71">
-        <v>539</v>
+        <v>1300</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233986</t>
+          <t xml:space="preserve">311242036</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-14</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,35 +4291,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnevej 6</t>
+          <t xml:space="preserve">Brolæggervej 1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9352</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190971</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H72">
-        <v>1694</v>
+        <v>1564</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234886</t>
+          <t xml:space="preserve">311242034</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-17</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusvej 1</t>
+          <t xml:space="preserve">Brolæggervej 1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,25 +4361,25 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3197319</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H73">
-        <v>3135</v>
+        <v>1241</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236938</t>
+          <t xml:space="preserve">311242038</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-27</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brolæggervej 4</t>
+          <t xml:space="preserve">Brolæggervej 1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,25 +4421,25 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7002091</t>
+          <t xml:space="preserve">3196572</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H74">
-        <v>322</v>
+        <v>259</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236928</t>
+          <t xml:space="preserve">311242031</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-27</t>
+          <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brolæggervej 1</t>
+          <t xml:space="preserve">Rådhuspladsen 1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">9285142</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="H75">
-        <v>1375</v>
+        <v>839</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242035</t>
+          <t xml:space="preserve">311243218</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brolæggervej 1</t>
+          <t xml:space="preserve">Understedvej 120</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">3194478</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,16 +4550,16 @@
         </is>
       </c>
       <c r="H76">
-        <v>516</v>
+        <v>306</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242033</t>
+          <t xml:space="preserve">311247877</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brolæggervej 1</t>
+          <t xml:space="preserve">Brøndenvej 1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9750</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">3193076</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>1300</v>
+        <v>4617</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242036</t>
+          <t xml:space="preserve">311248803</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brolæggervej 1</t>
+          <t xml:space="preserve">Brøndenvej 3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9750</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">3193076</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H78">
-        <v>1564</v>
+        <v>360</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242034</t>
+          <t xml:space="preserve">311248804</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,35 +4711,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brolæggervej 1</t>
+          <t xml:space="preserve">Hjørringvej 395</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9750</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">8274738</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H79">
-        <v>1241</v>
+        <v>1056</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242038</t>
+          <t xml:space="preserve">311248805</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,35 +4771,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brolæggervej 1</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196572</t>
+          <t xml:space="preserve">5510796</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>259</v>
+        <v>1418</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242031</t>
+          <t xml:space="preserve">311249789</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,35 +4831,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspladsen 1</t>
+          <t xml:space="preserve">Ternevej 5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9285142</t>
+          <t xml:space="preserve">5512953</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H81">
-        <v>839</v>
+        <v>919</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243218</t>
+          <t xml:space="preserve">311249785</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Understedvej 120</t>
+          <t xml:space="preserve">C. S. Møllers Vej 6</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3194478</t>
+          <t xml:space="preserve">5529697</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>306</v>
+        <v>488</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247877</t>
+          <t xml:space="preserve">311254528</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,17 +4951,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndenvej 1</t>
+          <t xml:space="preserve">Rimmens Alle 31</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9750</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3193076</t>
+          <t xml:space="preserve">5514238</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="H83">
-        <v>4617</v>
+        <v>292</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248803</t>
+          <t xml:space="preserve">311254530</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,35 +5011,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndenvej 3</t>
+          <t xml:space="preserve">Rimmens Alle 31</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9750</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3193076</t>
+          <t xml:space="preserve">5514238</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H84">
-        <v>360</v>
+        <v>1100</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248804</t>
+          <t xml:space="preserve">311254530</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,35 +5071,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjørringvej 395</t>
+          <t xml:space="preserve">Gl. Skolevej 25</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9750</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8274738</t>
+          <t xml:space="preserve">5515841</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H85">
-        <v>1056</v>
+        <v>402</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248805</t>
+          <t xml:space="preserve">311255688</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Gl. Skolevej 27</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5510796</t>
+          <t xml:space="preserve">5515841</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="H86">
-        <v>1418</v>
+        <v>309</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249789</t>
+          <t xml:space="preserve">311255688</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-24</t>
+          <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 5</t>
+          <t xml:space="preserve">L.P. Houmøllers Vej 19</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,25 +5201,25 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512953</t>
+          <t xml:space="preserve">8469815</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H87">
-        <v>919</v>
+        <v>788</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249785</t>
+          <t xml:space="preserve">311255690</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-24</t>
+          <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rimmens Alle 31</t>
+          <t xml:space="preserve">Sæbygårdvej 34</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5514238</t>
+          <t xml:space="preserve">3197368</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5270,16 +5270,16 @@
         </is>
       </c>
       <c r="H88">
-        <v>292</v>
+        <v>8714</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254530</t>
+          <t xml:space="preserve">311256859</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-16</t>
+          <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rimmens Alle 31</t>
+          <t xml:space="preserve">Ravnshøjvej 155</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,25 +5321,25 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5514238</t>
+          <t xml:space="preserve">3141803</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>1100</v>
+        <v>4131</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254530</t>
+          <t xml:space="preserve">311259615</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-16</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,35 +5371,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. S. Møllers Vej 6</t>
+          <t xml:space="preserve">Ravnshøjvej 155</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5529697</t>
+          <t xml:space="preserve">3141803</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H90">
-        <v>488</v>
+        <v>1383</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254528</t>
+          <t xml:space="preserve">311259615</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-16</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skolevej 27</t>
+          <t xml:space="preserve">Ravnshøjvej 155</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,25 +5441,25 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5515841</t>
+          <t xml:space="preserve">3141803</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H91">
-        <v>309</v>
+        <v>567</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255688</t>
+          <t xml:space="preserve">311259615</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,35 +5491,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skolevej 25</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5515841</t>
+          <t xml:space="preserve">8504590</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H92">
-        <v>402</v>
+        <v>1107</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255688</t>
+          <t xml:space="preserve">311259630</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,35 +5551,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">L.P. Houmøllers Vej 19</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8469815</t>
+          <t xml:space="preserve">8504590</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H93">
-        <v>788</v>
+        <v>1845</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255690</t>
+          <t xml:space="preserve">311259630</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,35 +5611,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæbygårdvej 34</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3197368</t>
+          <t xml:space="preserve">8504590</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H94">
-        <v>8714</v>
+        <v>874</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256859</t>
+          <t xml:space="preserve">311259630</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-27</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,30 +5671,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnshøjvej 155</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3141803</t>
+          <t xml:space="preserve">8504590</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H95">
-        <v>4131</v>
+        <v>483</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259615</t>
+          <t xml:space="preserve">311259630</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnshøjvej 155</t>
+          <t xml:space="preserve">Møllehus Alle 15</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3141803</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="H96">
-        <v>1383</v>
+        <v>1658</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259615</t>
+          <t xml:space="preserve">311260716</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnshøjvej 155</t>
+          <t xml:space="preserve">Søndergade 200</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,25 +5801,25 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3141803</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H97">
-        <v>567</v>
+        <v>2115</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259615</t>
+          <t xml:space="preserve">311260684</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,35 +5851,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Søndergade 200</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8504590</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H98">
-        <v>1107</v>
+        <v>499</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259630</t>
+          <t xml:space="preserve">311260724</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Søndergade 200</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8504590</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>1845</v>
+        <v>843</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259630</t>
+          <t xml:space="preserve">311260707</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Søndergade 200</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8504590</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="H100">
-        <v>874</v>
+        <v>539</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259630</t>
+          <t xml:space="preserve">311260710</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Søndergade 200</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8504590</t>
+          <t xml:space="preserve">1507019</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6050,16 +6050,16 @@
         </is>
       </c>
       <c r="H101">
-        <v>483</v>
+        <v>1207</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259630</t>
+          <t xml:space="preserve">311260714</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6106,15 +6106,15 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H102">
-        <v>2115</v>
+        <v>1987</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260684</t>
+          <t xml:space="preserve">311260718</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 200</t>
+          <t xml:space="preserve">Hybenvej 11</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">3190298</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>499</v>
+        <v>1742</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260724</t>
+          <t xml:space="preserve">311261818</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-20</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 200</t>
+          <t xml:space="preserve">Buhlsvej 19</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6221,25 +6221,25 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H104">
-        <v>843</v>
+        <v>1992</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260707</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 200</t>
+          <t xml:space="preserve">Buhlsvej 19</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H105">
-        <v>539</v>
+        <v>1106</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260710</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 200</t>
+          <t xml:space="preserve">Buhlsvej 19</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,25 +6341,25 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H106">
-        <v>1207</v>
+        <v>1300</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260714</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehus Alle 15</t>
+          <t xml:space="preserve">Buhlsvej 19</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,25 +6401,25 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H107">
-        <v>1658</v>
+        <v>1804</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260716</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 200</t>
+          <t xml:space="preserve">Buhlsvej 19</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,25 +6461,25 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507019</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H108">
-        <v>1987</v>
+        <v>433</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260718</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,35 +6511,35 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenvej 11</t>
+          <t xml:space="preserve">Buhlsvej 19</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190298</t>
+          <t xml:space="preserve">5520136</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H109">
-        <v>1742</v>
+        <v>433</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261818</t>
+          <t xml:space="preserve">311261999</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-20</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østkystvejen 314</t>
+          <t xml:space="preserve">Hybenvej 13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,20 +6581,20 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180907</t>
+          <t xml:space="preserve">3190217</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H110">
-        <v>1220</v>
+        <v>629</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311262055</t>
+          <t xml:space="preserve">311261981</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenvej 13</t>
+          <t xml:space="preserve">Østkystvejen 314</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,20 +6641,20 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190217</t>
+          <t xml:space="preserve">3180907</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H111">
-        <v>629</v>
+        <v>1220</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261981</t>
+          <t xml:space="preserve">311262055</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buhlsvej 19</t>
+          <t xml:space="preserve">Fasanvej 1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">5512816</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,16 +6710,16 @@
         </is>
       </c>
       <c r="H112">
-        <v>1992</v>
+        <v>1407</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261999</t>
+          <t xml:space="preserve">311278306</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-21</t>
+          <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,35 +6751,35 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buhlsvej 19</t>
+          <t xml:space="preserve">Engvej 10</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9982</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">7068864</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H113">
-        <v>1106</v>
+        <v>4025</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261999</t>
+          <t xml:space="preserve">311283499</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-21</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,35 +6811,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buhlsvej 19</t>
+          <t xml:space="preserve">Møldamvej 11</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9982</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">750358, 7068864</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H114">
-        <v>1300</v>
+        <v>2348</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261999</t>
+          <t xml:space="preserve">311283502</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-21</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,35 +6871,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buhlsvej 19</t>
+          <t xml:space="preserve">Skagavej 137</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">5532250</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H115">
-        <v>1804</v>
+        <v>368</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261999</t>
+          <t xml:space="preserve">311286112</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-21</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,35 +6931,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buhlsvej 19</t>
+          <t xml:space="preserve">Skagavej 139</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">5532250</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H116">
-        <v>433</v>
+        <v>5016</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261999</t>
+          <t xml:space="preserve">311286086</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-21</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,35 +6991,35 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buhlsvej 19</t>
+          <t xml:space="preserve">Skagavej 139</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5520136</t>
+          <t xml:space="preserve">5532250</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H117">
-        <v>433</v>
+        <v>1165</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261999</t>
+          <t xml:space="preserve">311286086</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-21</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,35 +7051,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fasanvej 1</t>
+          <t xml:space="preserve">Skagavej 139</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512816</t>
+          <t xml:space="preserve">5532250</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H118">
-        <v>1407</v>
+        <v>998</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278306</t>
+          <t xml:space="preserve">311286086</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-12</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,35 +7111,35 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 10</t>
+          <t xml:space="preserve">Skagavej 139</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9982</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7068864</t>
+          <t xml:space="preserve">5532250</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H119">
-        <v>4025</v>
+        <v>2308</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283502</t>
+          <t xml:space="preserve">311286086</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-13</t>
+          <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,35 +7171,35 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møldamvej 11</t>
+          <t xml:space="preserve">Kirkevej 29</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9982</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">750358, 7068864</t>
+          <t xml:space="preserve">5530935</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H120">
-        <v>2348</v>
+        <v>1108</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283502</t>
+          <t xml:space="preserve">311287044</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-13</t>
+          <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,35 +7231,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagavej 139</t>
+          <t xml:space="preserve">Sættravej 6</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5532250</t>
+          <t xml:space="preserve">3196599</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H121">
-        <v>5016</v>
+        <v>439</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286086</t>
+          <t xml:space="preserve">311296066</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2028-02-05</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagavej 139</t>
+          <t xml:space="preserve">Lindevej 13</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,25 +7301,25 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5532250</t>
+          <t xml:space="preserve">5533338</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H122">
-        <v>1165</v>
+        <v>332</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286086</t>
+          <t xml:space="preserve">311309873</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagavej 139</t>
+          <t xml:space="preserve">Trindelvej 6</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,25 +7361,25 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5532250</t>
+          <t xml:space="preserve">5534044</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H123">
-        <v>998</v>
+        <v>519</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286086</t>
+          <t xml:space="preserve">311309871</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,35 +7411,35 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagavej 139</t>
+          <t xml:space="preserve">Jyllandsgade 12</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5532250</t>
+          <t xml:space="preserve">5518731</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H124">
-        <v>2308</v>
+        <v>406</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286086</t>
+          <t xml:space="preserve">311310833</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2028-04-26</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,35 +7471,35 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagavej 137</t>
+          <t xml:space="preserve">Knivholtvej 20</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5532250</t>
+          <t xml:space="preserve">3147782</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H125">
-        <v>368</v>
+        <v>1823</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286112</t>
+          <t xml:space="preserve">311323733</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-28</t>
+          <t xml:space="preserve">2028-06-29</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,35 +7531,35 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 29</t>
+          <t xml:space="preserve">Arenfeldtsgade 20</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5530935</t>
+          <t xml:space="preserve">5510937</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H126">
-        <v>1108</v>
+        <v>2346</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287044</t>
+          <t xml:space="preserve">311325105</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-04</t>
+          <t xml:space="preserve">2028-07-06</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,35 +7591,35 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sættravej 6</t>
+          <t xml:space="preserve">Harald Nielsens Plads 7</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3196599</t>
+          <t xml:space="preserve">749488, 5518904</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H127">
-        <v>439</v>
+        <v>1046</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296066</t>
+          <t xml:space="preserve">311325419</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-05</t>
+          <t xml:space="preserve">2028-07-09</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,35 +7651,35 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 13</t>
+          <t xml:space="preserve">Peter Wessels Vej 49</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5533338</t>
+          <t xml:space="preserve">749487, 5518901</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H128">
-        <v>332</v>
+        <v>2270</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309873</t>
+          <t xml:space="preserve">311325422</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2028-07-09</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,17 +7711,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trindelvej 6</t>
+          <t xml:space="preserve">Rimmens Alle 35</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5534044</t>
+          <t xml:space="preserve">749486, 5518899</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7730,16 +7730,16 @@
         </is>
       </c>
       <c r="H129">
-        <v>519</v>
+        <v>2244</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309871</t>
+          <t xml:space="preserve">311325408</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2028-07-09</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jyllandsgade 12</t>
+          <t xml:space="preserve">Ingeborgvej 2</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518731</t>
+          <t xml:space="preserve">404174</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="H130">
-        <v>406</v>
+        <v>2096</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311310833</t>
+          <t xml:space="preserve">311341215</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-26</t>
+          <t xml:space="preserve">2028-10-12</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knivholtvej 20</t>
+          <t xml:space="preserve">Rådhus Alle 100</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3147782</t>
+          <t xml:space="preserve">5512231</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7850,16 +7850,16 @@
         </is>
       </c>
       <c r="H131">
-        <v>1823</v>
+        <v>12599</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323733</t>
+          <t xml:space="preserve">311486270</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-29</t>
+          <t xml:space="preserve">2031-01-07</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,35 +7891,35 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arenfeldtsgade 20</t>
+          <t xml:space="preserve">Strandvej 65</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9970</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5510937</t>
+          <t xml:space="preserve">402079</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H132">
-        <v>2346</v>
+        <v>788</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311325105</t>
+          <t xml:space="preserve">311568106</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-06</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,35 +7951,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rimmens Alle 35</t>
+          <t xml:space="preserve">Strandvej 65</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9970</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">749486, 5518899</t>
+          <t xml:space="preserve">402079</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H133">
-        <v>2244</v>
+        <v>662</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311325408</t>
+          <t xml:space="preserve">311568113</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-09</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Wessels Vej 49</t>
+          <t xml:space="preserve">Cronborgvej 20</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">749487, 5518901</t>
+          <t xml:space="preserve">7428551</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>2270</v>
+        <v>1181</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311325422</t>
+          <t xml:space="preserve">311641669</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-09</t>
+          <t xml:space="preserve">2032-11-09</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Nielsens Plads 7</t>
+          <t xml:space="preserve">Rådhus Alle 98</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">749488, 5518904</t>
+          <t xml:space="preserve">5512255</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H135">
-        <v>1046</v>
+        <v>2397</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311325419</t>
+          <t xml:space="preserve">311643201</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-09</t>
+          <t xml:space="preserve">2032-11-17</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,17 +8131,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhus Alle 100</t>
+          <t xml:space="preserve">Rebslagervej 1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9300</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512231</t>
+          <t xml:space="preserve">8986950</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8150,16 +8150,16 @@
         </is>
       </c>
       <c r="H136">
-        <v>12599</v>
+        <v>350</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311486270</t>
+          <t xml:space="preserve">311645860</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-07</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,35 +8191,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cronborgvej 20</t>
+          <t xml:space="preserve">Skansegade 12C</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7428551</t>
+          <t xml:space="preserve">5511973</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H137">
-        <v>1181</v>
+        <v>362</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641669</t>
+          <t xml:space="preserve">311650125</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-09</t>
+          <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhus Alle 98</t>
+          <t xml:space="preserve">Anholtvej 4</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8261,25 +8261,25 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512255</t>
+          <t xml:space="preserve">401514, 401515</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H138">
-        <v>2397</v>
+        <v>1029</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643201</t>
+          <t xml:space="preserve">311651062</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-17</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,35 +8311,35 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rebslagervej 1</t>
+          <t xml:space="preserve">Hans Baghs Vej 27</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8986950</t>
+          <t xml:space="preserve">100047969</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H139">
-        <v>350</v>
+        <v>578</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645860</t>
+          <t xml:space="preserve">311650919</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skansegade 12C</t>
+          <t xml:space="preserve">Peter Wessels Vej 40</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5511973</t>
+          <t xml:space="preserve">100051897</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="H140">
-        <v>362</v>
+        <v>1610</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650125</t>
+          <t xml:space="preserve">311650920</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-19</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,30 +8431,30 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Baghs Vej 27</t>
+          <t xml:space="preserve">Rimmens Alle 75</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047969</t>
+          <t xml:space="preserve">5518900</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H141">
-        <v>578</v>
+        <v>14065</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650919</t>
+          <t xml:space="preserve">311650905</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Wessels Vej 40</t>
+          <t xml:space="preserve">Toftegårdsvej 48</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051897</t>
+          <t xml:space="preserve">100085261</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8510,11 +8510,11 @@
         </is>
       </c>
       <c r="H142">
-        <v>1610</v>
+        <v>561</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650920</t>
+          <t xml:space="preserve">311650921</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftegårdsvej 48</t>
+          <t xml:space="preserve">H.C. Ørsteds Vej 35</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">100085261</t>
+          <t xml:space="preserve">5518015</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8570,16 +8570,16 @@
         </is>
       </c>
       <c r="H143">
-        <v>561</v>
+        <v>1851</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650921</t>
+          <t xml:space="preserve">311670495</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rimmens Alle 75</t>
+          <t xml:space="preserve">H.C. Ørsteds Vej 35</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8621,25 +8621,25 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518900</t>
+          <t xml:space="preserve">5518015</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H144">
-        <v>14065</v>
+        <v>355</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650905</t>
+          <t xml:space="preserve">311670497</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Ørsteds Vej 35</t>
+          <t xml:space="preserve">Caspersvej 7</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518015</t>
+          <t xml:space="preserve">403766, 403767, 403768, 403769</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="H145">
-        <v>1851</v>
+        <v>5954</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670495</t>
+          <t xml:space="preserve">311703838</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-08-30</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Ørsteds Vej 35</t>
+          <t xml:space="preserve">Jyllandsgade 4B</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,25 +8741,25 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518015</t>
+          <t xml:space="preserve">5518894</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H146">
-        <v>355</v>
+        <v>1427</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670497</t>
+          <t xml:space="preserve">311713408</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-10-09</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,17 +8791,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jyllandsgade 4B</t>
+          <t xml:space="preserve">Chr. Xs Vej 52</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9900</t>
+          <t xml:space="preserve">9990</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518894</t>
+          <t xml:space="preserve">5530956</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8810,16 +8810,16 @@
         </is>
       </c>
       <c r="H147">
-        <v>1427</v>
+        <v>1200</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311713408</t>
+          <t xml:space="preserve">311714383</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-09</t>
+          <t xml:space="preserve">2033-10-11</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,35 +8851,35 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chr. Xs Vej 52</t>
+          <t xml:space="preserve">Markedsvej 46</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990</t>
+          <t xml:space="preserve">9900</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5530956</t>
+          <t xml:space="preserve">5511030</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H148">
-        <v>1200</v>
+        <v>458</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311714383</t>
+          <t xml:space="preserve">311715531</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-11</t>
+          <t xml:space="preserve">2033-10-17</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markedsvej 46</t>
+          <t xml:space="preserve">Skansegade 2</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8921,25 +8921,25 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5511030</t>
+          <t xml:space="preserve">5511948</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H149">
-        <v>458</v>
+        <v>368</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311715531</t>
+          <t xml:space="preserve">311724881</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-17</t>
+          <t xml:space="preserve">2033-11-27</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skansegade 2</t>
+          <t xml:space="preserve">L.P. Houmøllers Vej 88</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5511948</t>
+          <t xml:space="preserve">401477, 401478</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8990,16 +8990,16 @@
         </is>
       </c>
       <c r="H150">
-        <v>368</v>
+        <v>1284</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724881</t>
+          <t xml:space="preserve">311730087</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-27</t>
+          <t xml:space="preserve">2033-12-19</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oliepieren 7</t>
+          <t xml:space="preserve">Færgehavnsvej 16</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9166,11 +9166,11 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
       <c r="H153">
-        <v>1055</v>
+        <v>1127</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færgehavnsvej 16</t>
+          <t xml:space="preserve">Færgehavnsvej 26</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,16 +9221,16 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202337</t>
+          <t xml:space="preserve">750051, 10202337</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="H154">
-        <v>1127</v>
+        <v>306</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pier 5 2</t>
+          <t xml:space="preserve">Færgehavnsvej 29</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,16 +9281,16 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202337</t>
+          <t xml:space="preserve">749790, 10202337</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="H155">
-        <v>1530</v>
+        <v>531</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandholm 57</t>
+          <t xml:space="preserve">Oliepieren 7</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,16 +9341,16 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202337, 100800984</t>
+          <t xml:space="preserve">10202337</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H156">
-        <v>627</v>
+        <v>1055</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færgehavnsvej 29</t>
+          <t xml:space="preserve">Pier 5 2</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9401,16 +9401,16 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">749790, 10202337</t>
+          <t xml:space="preserve">10202337</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H157">
-        <v>531</v>
+        <v>1530</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færgehavnsvej 26</t>
+          <t xml:space="preserve">Sandholm 57</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9461,16 +9461,16 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">750051, 10202337</t>
+          <t xml:space="preserve">10202337, 100800984</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="H158">
-        <v>306</v>
+        <v>627</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311777397</t>
+          <t xml:space="preserve">311777393</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 6</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10726,15 +10726,15 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H179">
-        <v>489</v>
+        <v>1662</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898286</t>
+          <t xml:space="preserve">311898284</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10786,15 +10786,15 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H180">
-        <v>1662</v>
+        <v>491</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898284</t>
+          <t xml:space="preserve">311898281</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10846,15 +10846,15 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H181">
-        <v>491</v>
+        <v>939</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898281</t>
+          <t xml:space="preserve">311898291</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10906,11 +10906,11 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H182">
-        <v>939</v>
+        <v>520</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -10966,11 +10966,11 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H183">
-        <v>520</v>
+        <v>2079</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Skolevej 6</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11026,15 +11026,15 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H184">
-        <v>2079</v>
+        <v>489</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898291</t>
+          <t xml:space="preserve">311898286</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">

--- a/public/exports/29189498.xlsx
+++ b/public/exports/29189498.xlsx
@@ -5334,7 +5334,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259615</t>
+          <t xml:space="preserve">311259621</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259615</t>
+          <t xml:space="preserve">311259621</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259615</t>
+          <t xml:space="preserve">311259621</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283499</t>
+          <t xml:space="preserve">311283502</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311777393</t>
+          <t xml:space="preserve">311777396</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">

--- a/public/exports/29189498.xlsx
+++ b/public/exports/29189498.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L185"/>
+  <dimension ref="A1:M185"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">NIRAS A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-14</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-19</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-09</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-24</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRANEKAER-ARKITEKTKONTOR.DK</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-02-05</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-17</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-07</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-14</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-14</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-17</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-20</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5334,20 +5774,25 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259621</t>
+          <t xml:space="preserve">311259615</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5394,20 +5839,25 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259621</t>
+          <t xml:space="preserve">311259615</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5454,20 +5904,25 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259621</t>
+          <t xml:space="preserve">311259615</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-20</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-12</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-28</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-05</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-26</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-29</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-06</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-09</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-09</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-09</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-12</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-07</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-09</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-17</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-30</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-09</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kinnerup Rådgivende Ingeniør</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-11</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-17</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-27</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-19</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-05</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-29</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-11</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-15</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-15</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-06</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,21 +12019,26 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-11</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L185"/>
+  <autoFilter ref="A1:M185"/>
 </worksheet>
 </file>
--- a/public/exports/29189498.xlsx
+++ b/public/exports/29189498.xlsx
@@ -7334,7 +7334,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283502</t>
+          <t xml:space="preserve">311283499</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311777396</t>
+          <t xml:space="preserve">311777393</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Husplan ApS</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
